--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -1,108 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Modal shift/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853AEB87-2AD3-4841-8B1A-6FE6554CE8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -271,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,83 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>11764.024999999991</v>
+        <v>15083.906</v>
       </c>
       <c r="C2">
-        <v>11226.976000000001</v>
+        <v>14388.749</v>
       </c>
       <c r="D2">
-        <v>12353.519</v>
+        <v>15821.638</v>
       </c>
       <c r="E2">
-        <v>116812.696</v>
+        <v>128983.4859999999</v>
       </c>
       <c r="F2">
-        <v>114631.931</v>
+        <v>126697.383</v>
       </c>
       <c r="G2">
-        <v>119149.17200000001</v>
+        <v>131409.89</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -535,200 +455,210 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>15536600126.063</v>
+        <v>17156607778.19</v>
       </c>
       <c r="L2">
-        <v>15246777407.965</v>
+        <v>16858862420.94901</v>
       </c>
       <c r="M2">
-        <v>15849534998.181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>17476014063.552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>9837.0099999999948</v>
+        <v>10895.53</v>
       </c>
       <c r="C3">
-        <v>9514.599000000002</v>
+        <v>10577.876</v>
       </c>
       <c r="D3">
-        <v>10165.268</v>
+        <v>11214.25900000001</v>
       </c>
       <c r="E3">
-        <v>8574.5060000000012</v>
+        <v>14685.25999999999</v>
       </c>
       <c r="F3">
-        <v>8345.2019999999975</v>
+        <v>14312.916</v>
       </c>
       <c r="G3">
-        <v>8799.9510000000009</v>
+        <v>15078.801</v>
       </c>
       <c r="H3">
-        <v>547859793.70000029</v>
+        <v>573989396.2959998</v>
       </c>
       <c r="I3">
-        <v>530428010.97500008</v>
+        <v>557250175.207</v>
       </c>
       <c r="J3">
-        <v>566462290.85300016</v>
+        <v>591928555.6310003</v>
       </c>
       <c r="K3">
-        <v>1139888078.4519999</v>
+        <v>1953697196.575</v>
       </c>
       <c r="L3">
-        <v>1110942512.516</v>
+        <v>1903182836.175</v>
       </c>
       <c r="M3">
-        <v>1170416768.516999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>2003875081.062</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>8637.2830000000031</v>
+        <v>2561.512000000001</v>
       </c>
       <c r="C4">
-        <v>8384.1269999999968</v>
+        <v>2488.349</v>
       </c>
       <c r="D4">
-        <v>8906.9830000000002</v>
+        <v>2637.839</v>
       </c>
       <c r="E4">
-        <v>13058.022000000001</v>
+        <v>1196.856</v>
       </c>
       <c r="F4">
-        <v>12515.109</v>
+        <v>1164.824000000001</v>
       </c>
       <c r="G4">
-        <v>13613.314</v>
+        <v>1230.714</v>
       </c>
       <c r="H4">
-        <v>127920587.883</v>
+        <v>75123430.97000003</v>
       </c>
       <c r="I4">
-        <v>124051264.853</v>
+        <v>72976689.87799999</v>
       </c>
       <c r="J4">
-        <v>131892757.55400001</v>
+        <v>77315340.50199997</v>
       </c>
       <c r="K4">
-        <v>1736176681.174</v>
+        <v>159167336.474</v>
       </c>
       <c r="L4">
-        <v>1670253278.349</v>
+        <v>154894223.841</v>
       </c>
       <c r="M4">
-        <v>1810067213.433001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>163532722.758</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>1743.229</v>
+        <v>1655.075</v>
       </c>
       <c r="C5">
-        <v>1687.721</v>
+        <v>1612.089000000001</v>
       </c>
       <c r="D5">
-        <v>1796.803000000001</v>
+        <v>1700.135</v>
       </c>
       <c r="E5">
-        <v>3401.0839999999989</v>
+        <v>3145.646999999999</v>
       </c>
       <c r="F5">
-        <v>3284.0379999999991</v>
+        <v>3064.217999999999</v>
       </c>
       <c r="G5">
-        <v>3518.219000000001</v>
+        <v>3227.782999999999</v>
       </c>
       <c r="H5">
-        <v>131017505.138</v>
+        <v>64878142.93399999</v>
       </c>
       <c r="I5">
-        <v>126982695.595</v>
+        <v>63252576.57200003</v>
       </c>
       <c r="J5">
-        <v>135351726.447</v>
+        <v>66672747.98200002</v>
       </c>
       <c r="K5">
-        <v>452012968.61399978</v>
+        <v>418383080.191</v>
       </c>
       <c r="L5">
-        <v>436662147.87100011</v>
+        <v>407490928.49</v>
       </c>
       <c r="M5">
-        <v>468293886.36100012</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>429227546.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>3459.2540000000008</v>
+        <v>3956.688</v>
       </c>
       <c r="C6">
-        <v>3282.7459999999992</v>
+        <v>3775.784</v>
       </c>
       <c r="D6">
-        <v>3647.2520000000022</v>
+        <v>4144.503999999999</v>
       </c>
       <c r="E6">
-        <v>5520.523000000001</v>
+        <v>4518.412000000002</v>
       </c>
       <c r="F6">
-        <v>5332.148000000001</v>
+        <v>4312.114000000001</v>
       </c>
       <c r="G6">
-        <v>5715.9570000000022</v>
+        <v>4745.686000000002</v>
       </c>
       <c r="H6">
-        <v>58237615.697000027</v>
+        <v>65857107.546</v>
       </c>
       <c r="I6">
-        <v>55248297.492000014</v>
+        <v>62905739.92899999</v>
       </c>
       <c r="J6">
-        <v>61338518.734999977</v>
+        <v>68992358.095</v>
       </c>
       <c r="K6">
-        <v>733643839.74700022</v>
+        <v>600805060.2479999</v>
       </c>
       <c r="L6">
-        <v>708958391.75500011</v>
+        <v>573206688.5310001</v>
       </c>
       <c r="M6">
-        <v>760624801.39499998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>630601297.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>33349.503000000012</v>
+        <v>36965.158</v>
       </c>
       <c r="C7">
-        <v>32534.48000000001</v>
+        <v>36123.99100000001</v>
       </c>
       <c r="D7">
-        <v>34180.931000000011</v>
+        <v>37803.003</v>
       </c>
       <c r="E7">
-        <v>10644.380999999999</v>
+        <v>13251.298</v>
       </c>
       <c r="F7">
-        <v>10288.785</v>
+        <v>12862.28</v>
       </c>
       <c r="G7">
-        <v>11000.962</v>
+        <v>13647.36</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -740,95 +670,99 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1416012130.1559989</v>
+        <v>1762048063.399</v>
       </c>
       <c r="L7">
-        <v>1369206636.319</v>
+        <v>1709756456.058</v>
       </c>
       <c r="M7">
-        <v>1463919239.6340001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>1818482671.981</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chronic diseases</t>
+        </is>
       </c>
       <c r="B8">
-        <v>57026.27900000001</v>
+        <v>19068.80499999999</v>
       </c>
       <c r="C8">
-        <v>55403.672999999981</v>
+        <v>18454.09800000001</v>
       </c>
       <c r="D8">
-        <v>58697.237000000023</v>
+        <v>19696.73700000001</v>
       </c>
       <c r="E8">
-        <v>41198.516000000003</v>
+        <v>23546.175</v>
       </c>
       <c r="F8">
-        <v>39765.282000000007</v>
+        <v>22854.07200000001</v>
       </c>
       <c r="G8">
-        <v>42648.402999999991</v>
+        <v>24282.984</v>
       </c>
       <c r="H8">
-        <v>865035502.41800117</v>
+        <v>779848077.7459998</v>
       </c>
       <c r="I8">
-        <v>836710268.91499996</v>
+        <v>756385181.586</v>
       </c>
       <c r="J8">
-        <v>895045293.58899975</v>
+        <v>804909002.21</v>
       </c>
       <c r="K8">
-        <v>5477733698.1429977</v>
+        <v>3132052673.487997</v>
       </c>
       <c r="L8">
-        <v>5296022966.8099976</v>
+        <v>3038774677.037001</v>
       </c>
       <c r="M8">
-        <v>5673321909.3400002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>3227236647.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>68790.304000000004</v>
+        <v>71117.86900000001</v>
       </c>
       <c r="C9">
-        <v>66630.649000000034</v>
+        <v>68966.83799999999</v>
       </c>
       <c r="D9">
-        <v>71050.755999999994</v>
+        <v>73321.378</v>
       </c>
       <c r="E9">
-        <v>158011.21200000009</v>
+        <v>165780.9589999999</v>
       </c>
       <c r="F9">
-        <v>154397.21299999999</v>
+        <v>162413.7350000001</v>
       </c>
       <c r="G9">
-        <v>161797.57499999981</v>
+        <v>169340.2340000001</v>
       </c>
       <c r="H9">
-        <v>865035502.41800117</v>
+        <v>779848077.7459998</v>
       </c>
       <c r="I9">
-        <v>836710268.91499996</v>
+        <v>756385181.586</v>
       </c>
       <c r="J9">
-        <v>895045293.58899975</v>
+        <v>804909002.21</v>
       </c>
       <c r="K9">
-        <v>21014333824.206009</v>
+        <v>22050708515.077</v>
       </c>
       <c r="L9">
-        <v>20542800374.775009</v>
+        <v>21607393554.04402</v>
       </c>
       <c r="M9">
-        <v>21522856907.521</v>
+        <v>22521733383.123</v>
       </c>
     </row>
   </sheetData>
